--- a/case_studies/high_feedstock_availability_10_dd/2040/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_10_dd/2040/technologies.xlsx
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -694,7 +694,7 @@
         <v>115.62</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>234</v>
+        <v>233.99</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>85.06</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>7.07</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         <v>89.48999999999999</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>-0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
